--- a/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
+++ b/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\ME\trans\VSbS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathaniyer/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/ME/trans/VSbS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D14C0B5A-7CB1-4CFE-A108-6B7460C2BDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F136E0E7-A251-0841-9C53-65F72D95EE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1110" windowWidth="13035" windowHeight="16890" firstSheet="2" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="13840" windowHeight="12640" firstSheet="1" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -1632,9 +1631,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B0F8C0-DE1A-4000-9351-A11EE8CD5BC4}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="70.140625" customWidth="1"/>
+    <col min="2" max="2" width="70.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1645,7 +1644,7 @@
         <v>108</v>
       </c>
       <c r="C1" s="104">
-        <v>45258</v>
+        <v>45295</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1758,14 +1757,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949F6402-DD66-4CAC-8910-748EA4AEB83B}">
   <dimension ref="A1:P63"/>
-  <sheetFormatPr defaultRowHeight="8.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="10"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="4" customWidth="1"/>
-    <col min="2" max="16" width="9.85546875" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="11.33203125" style="4" customWidth="1"/>
+    <col min="2" max="16" width="9.83203125" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15">
+    <row r="1" spans="1:16" ht="14">
       <c r="A1" s="106" t="s">
         <v>76</v>
       </c>
@@ -1803,7 +1802,7 @@
       <c r="O2" s="96"/>
       <c r="P2" s="96"/>
     </row>
-    <row r="3" spans="1:16" ht="9">
+    <row r="3" spans="1:16" ht="11">
       <c r="A3" s="97" t="s">
         <v>75</v>
       </c>
@@ -1845,7 +1844,7 @@
       <c r="O4" s="108"/>
       <c r="P4" s="109"/>
     </row>
-    <row r="5" spans="1:16" ht="9">
+    <row r="5" spans="1:16" ht="11">
       <c r="A5" s="79"/>
       <c r="B5" s="110" t="s">
         <v>73</v>
@@ -1873,7 +1872,7 @@
       <c r="O5" s="111"/>
       <c r="P5" s="114"/>
     </row>
-    <row r="6" spans="1:16" ht="9">
+    <row r="6" spans="1:16" ht="11">
       <c r="A6" s="79" t="s">
         <v>68</v>
       </c>
@@ -1901,7 +1900,7 @@
       <c r="O6" s="88"/>
       <c r="P6" s="87"/>
     </row>
-    <row r="7" spans="1:16" ht="9">
+    <row r="7" spans="1:16" ht="11">
       <c r="A7" s="79"/>
       <c r="B7" s="79" t="s">
         <v>63</v>
@@ -1947,7 +1946,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="9">
+    <row r="8" spans="1:16" ht="11">
       <c r="A8" s="79"/>
       <c r="B8" s="79" t="s">
         <v>65</v>
@@ -1995,7 +1994,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="9">
+    <row r="9" spans="1:16" ht="11">
       <c r="A9" s="74"/>
       <c r="B9" s="74" t="s">
         <v>60</v>
@@ -2035,7 +2034,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="9">
+    <row r="10" spans="1:16" ht="11">
       <c r="A10" s="19" t="s">
         <v>58</v>
       </c>
@@ -2085,7 +2084,7 @@
         <v>5320340</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="9">
+    <row r="11" spans="1:16" ht="11">
       <c r="A11" s="19" t="s">
         <v>57</v>
       </c>
@@ -2135,7 +2134,7 @@
         <v>792826</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="9">
+    <row r="12" spans="1:16" ht="11">
       <c r="A12" s="19" t="s">
         <v>56</v>
       </c>
@@ -2185,7 +2184,7 @@
         <v>6053781</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="9">
+    <row r="13" spans="1:16" ht="11">
       <c r="A13" s="19" t="s">
         <v>55</v>
       </c>
@@ -2235,7 +2234,7 @@
         <v>2913369</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="9">
+    <row r="14" spans="1:16" ht="11">
       <c r="A14" s="52" t="s">
         <v>54</v>
       </c>
@@ -2285,7 +2284,7 @@
         <v>30398249</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="9">
+    <row r="15" spans="1:16" ht="11">
       <c r="A15" s="19" t="s">
         <v>53</v>
       </c>
@@ -2335,7 +2334,7 @@
         <v>5350708</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="9">
+    <row r="16" spans="1:16" ht="11">
       <c r="A16" s="19" t="s">
         <v>52</v>
       </c>
@@ -2385,7 +2384,7 @@
         <v>2867554</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="9">
+    <row r="17" spans="1:16" ht="11">
       <c r="A17" s="43" t="s">
         <v>51</v>
       </c>
@@ -2435,7 +2434,7 @@
         <v>1006135</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="9">
+    <row r="18" spans="1:16" ht="11">
       <c r="A18" s="19" t="s">
         <v>50</v>
       </c>
@@ -2485,7 +2484,7 @@
         <v>356537</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="9">
+    <row r="19" spans="1:16" ht="11">
       <c r="A19" s="19" t="s">
         <v>49</v>
       </c>
@@ -2535,7 +2534,7 @@
         <v>18464506</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="9">
+    <row r="20" spans="1:16" ht="11">
       <c r="A20" s="19" t="s">
         <v>48</v>
       </c>
@@ -2585,7 +2584,7 @@
         <v>8829596</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="9">
+    <row r="21" spans="1:16" ht="11">
       <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
@@ -2635,7 +2634,7 @@
         <v>1244935</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="9">
+    <row r="22" spans="1:16" ht="11">
       <c r="A22" s="52" t="s">
         <v>46</v>
       </c>
@@ -2685,7 +2684,7 @@
         <v>1917677</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="9">
+    <row r="23" spans="1:16" ht="11">
       <c r="A23" s="19" t="s">
         <v>45</v>
       </c>
@@ -2735,7 +2734,7 @@
         <v>10587725</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="9">
+    <row r="24" spans="1:16" ht="11">
       <c r="A24" s="19" t="s">
         <v>44</v>
       </c>
@@ -2785,7 +2784,7 @@
         <v>6199901</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="9">
+    <row r="25" spans="1:16" ht="11">
       <c r="A25" s="43" t="s">
         <v>43</v>
       </c>
@@ -2835,7 +2834,7 @@
         <v>3787224</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="9">
+    <row r="26" spans="1:16" ht="11">
       <c r="A26" s="19" t="s">
         <v>42</v>
       </c>
@@ -2885,7 +2884,7 @@
         <v>2603543</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="9">
+    <row r="27" spans="1:16" ht="11">
       <c r="A27" s="19" t="s">
         <v>41</v>
       </c>
@@ -2935,7 +2934,7 @@
         <v>4459685</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="9">
+    <row r="28" spans="1:16" ht="11">
       <c r="A28" s="19" t="s">
         <v>40</v>
       </c>
@@ -2985,7 +2984,7 @@
         <v>3861204</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="9">
+    <row r="29" spans="1:16" ht="11">
       <c r="A29" s="19" t="s">
         <v>39</v>
       </c>
@@ -3035,7 +3034,7 @@
         <v>1121106</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="9">
+    <row r="30" spans="1:16" ht="11">
       <c r="A30" s="52" t="s">
         <v>38</v>
       </c>
@@ -3085,7 +3084,7 @@
         <v>4211377</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="9">
+    <row r="31" spans="1:16" ht="11">
       <c r="A31" s="19" t="s">
         <v>37</v>
       </c>
@@ -3135,7 +3134,7 @@
         <v>5036686</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="9">
+    <row r="32" spans="1:16" ht="11">
       <c r="A32" s="19" t="s">
         <v>36</v>
       </c>
@@ -3185,7 +3184,7 @@
         <v>8453239</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="9">
+    <row r="33" spans="1:16" ht="11">
       <c r="A33" s="43" t="s">
         <v>35</v>
       </c>
@@ -3235,7 +3234,7 @@
         <v>5690749</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="9">
+    <row r="34" spans="1:16" ht="11">
       <c r="A34" s="19" t="s">
         <v>34</v>
       </c>
@@ -3285,7 +3284,7 @@
         <v>2058975</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="9">
+    <row r="35" spans="1:16" ht="11">
       <c r="A35" s="19" t="s">
         <v>33</v>
       </c>
@@ -3335,7 +3334,7 @@
         <v>5587022</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="9">
+    <row r="36" spans="1:16" ht="11">
       <c r="A36" s="19" t="s">
         <v>32</v>
       </c>
@@ -3385,7 +3384,7 @@
         <v>1952553</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="9">
+    <row r="37" spans="1:16" ht="11">
       <c r="A37" s="19" t="s">
         <v>31</v>
       </c>
@@ -3435,7 +3434,7 @@
         <v>1935357</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="9">
+    <row r="38" spans="1:16" ht="11">
       <c r="A38" s="52" t="s">
         <v>30</v>
       </c>
@@ -3485,7 +3484,7 @@
         <v>2549357</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="9">
+    <row r="39" spans="1:16" ht="11">
       <c r="A39" s="19" t="s">
         <v>29</v>
       </c>
@@ -3535,7 +3534,7 @@
         <v>1357535</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="9">
+    <row r="40" spans="1:16" ht="11">
       <c r="A40" s="19" t="s">
         <v>28</v>
       </c>
@@ -3585,7 +3584,7 @@
         <v>6006247</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="9">
+    <row r="41" spans="1:16" ht="11">
       <c r="A41" s="43" t="s">
         <v>27</v>
       </c>
@@ -3635,7 +3634,7 @@
         <v>1783151</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="9">
+    <row r="42" spans="1:16" ht="11">
       <c r="A42" s="19" t="s">
         <v>26</v>
       </c>
@@ -3685,7 +3684,7 @@
         <v>11324755</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="9">
+    <row r="43" spans="1:16" ht="11">
       <c r="A43" s="19" t="s">
         <v>25</v>
       </c>
@@ -3735,7 +3734,7 @@
         <v>8739280</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="9">
+    <row r="44" spans="1:16" ht="11">
       <c r="A44" s="19" t="s">
         <v>24</v>
       </c>
@@ -3785,7 +3784,7 @@
         <v>899083</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="9">
+    <row r="45" spans="1:16" ht="11">
       <c r="A45" s="19" t="s">
         <v>23</v>
       </c>
@@ -3835,7 +3834,7 @@
         <v>10592317</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="9">
+    <row r="46" spans="1:16" ht="11">
       <c r="A46" s="52" t="s">
         <v>22</v>
       </c>
@@ -3885,7 +3884,7 @@
         <v>3730247</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="9">
+    <row r="47" spans="1:16" ht="11">
       <c r="A47" s="19" t="s">
         <v>21</v>
       </c>
@@ -3935,7 +3934,7 @@
         <v>4095442</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="9">
+    <row r="48" spans="1:16" ht="11">
       <c r="A48" s="19" t="s">
         <v>20</v>
       </c>
@@ -3985,7 +3984,7 @@
         <v>10690187</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="9">
+    <row r="49" spans="1:16" ht="11">
       <c r="A49" s="43" t="s">
         <v>19</v>
       </c>
@@ -4035,7 +4034,7 @@
         <v>866625</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="9">
+    <row r="50" spans="1:16" ht="11">
       <c r="A50" s="19" t="s">
         <v>18</v>
       </c>
@@ -4085,7 +4084,7 @@
         <v>4561299</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="9">
+    <row r="51" spans="1:16" ht="11">
       <c r="A51" s="19" t="s">
         <v>17</v>
       </c>
@@ -4135,7 +4134,7 @@
         <v>1294282</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="9">
+    <row r="52" spans="1:16" ht="11">
       <c r="A52" s="19" t="s">
         <v>16</v>
       </c>
@@ -4185,7 +4184,7 @@
         <v>5855373</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="9">
+    <row r="53" spans="1:16" ht="11">
       <c r="A53" s="19" t="s">
         <v>15</v>
       </c>
@@ -4235,7 +4234,7 @@
         <v>22419490</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="9">
+    <row r="54" spans="1:16" ht="11">
       <c r="A54" s="52" t="s">
         <v>14</v>
       </c>
@@ -4285,7 +4284,7 @@
         <v>2479604</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="9">
+    <row r="55" spans="1:16" ht="11">
       <c r="A55" s="19" t="s">
         <v>13</v>
       </c>
@@ -4335,7 +4334,7 @@
         <v>607890</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="9">
+    <row r="56" spans="1:16" ht="11">
       <c r="A56" s="19" t="s">
         <v>12</v>
       </c>
@@ -4385,7 +4384,7 @@
         <v>7606452</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="9">
+    <row r="57" spans="1:16" ht="11">
       <c r="A57" s="43" t="s">
         <v>11</v>
       </c>
@@ -4435,7 +4434,7 @@
         <v>7257401</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="9">
+    <row r="58" spans="1:16" ht="11">
       <c r="A58" s="19" t="s">
         <v>10</v>
       </c>
@@ -4485,7 +4484,7 @@
         <v>1657362</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="9">
+    <row r="59" spans="1:16" ht="11">
       <c r="A59" s="19" t="s">
         <v>9</v>
       </c>
@@ -4535,7 +4534,7 @@
         <v>5616271</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="9">
+    <row r="60" spans="1:16" ht="11">
       <c r="A60" s="19" t="s">
         <v>8</v>
       </c>
@@ -4585,7 +4584,7 @@
         <v>861028</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="9">
+    <row r="61" spans="1:16" ht="11">
       <c r="A61" s="11" t="s">
         <v>7</v>
       </c>
@@ -4635,7 +4634,7 @@
         <v>275913237</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="9">
+    <row r="62" spans="1:16" ht="11">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -4653,7 +4652,7 @@
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
     </row>
-    <row r="63" spans="1:16" ht="39.6" customHeight="1">
+    <row r="63" spans="1:16" ht="39.5" customHeight="1">
       <c r="A63" s="105" t="s">
         <v>6</v>
       </c>
@@ -4725,10 +4724,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.7109375" customWidth="1"/>
+    <col min="2" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6146,10 +6145,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.7109375" customWidth="1"/>
+    <col min="2" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">

--- a/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
+++ b/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathaniyer/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/ME/trans/VSbS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\ME\trans\VSbS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F136E0E7-A251-0841-9C53-65F72D95EE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D86F122-12C8-40C0-A478-77E0089C511D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="13840" windowHeight="12640" firstSheet="1" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12510" firstSheet="1" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1334,9 +1334,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1374,7 +1374,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1480,7 +1480,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1622,7 +1622,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1631,9 +1631,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B0F8C0-DE1A-4000-9351-A11EE8CD5BC4}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="70.1640625" customWidth="1"/>
+    <col min="2" max="2" width="70.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1644,7 +1644,7 @@
         <v>108</v>
       </c>
       <c r="C1" s="104">
-        <v>45295</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1757,14 +1757,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949F6402-DD66-4CAC-8910-748EA4AEB83B}">
   <dimension ref="A1:P63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="10"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="4" customWidth="1"/>
-    <col min="2" max="16" width="9.83203125" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="9.1640625" style="4"/>
+    <col min="1" max="1" width="11.28515625" style="4" customWidth="1"/>
+    <col min="2" max="16" width="9.85546875" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14">
+    <row r="1" spans="1:16" ht="15">
       <c r="A1" s="106" t="s">
         <v>76</v>
       </c>
@@ -1802,7 +1802,7 @@
       <c r="O2" s="96"/>
       <c r="P2" s="96"/>
     </row>
-    <row r="3" spans="1:16" ht="11">
+    <row r="3" spans="1:16" ht="9">
       <c r="A3" s="97" t="s">
         <v>75</v>
       </c>
@@ -1844,7 +1844,7 @@
       <c r="O4" s="108"/>
       <c r="P4" s="109"/>
     </row>
-    <row r="5" spans="1:16" ht="11">
+    <row r="5" spans="1:16" ht="9">
       <c r="A5" s="79"/>
       <c r="B5" s="110" t="s">
         <v>73</v>
@@ -1872,7 +1872,7 @@
       <c r="O5" s="111"/>
       <c r="P5" s="114"/>
     </row>
-    <row r="6" spans="1:16" ht="11">
+    <row r="6" spans="1:16" ht="9">
       <c r="A6" s="79" t="s">
         <v>68</v>
       </c>
@@ -1900,7 +1900,7 @@
       <c r="O6" s="88"/>
       <c r="P6" s="87"/>
     </row>
-    <row r="7" spans="1:16" ht="11">
+    <row r="7" spans="1:16" ht="9">
       <c r="A7" s="79"/>
       <c r="B7" s="79" t="s">
         <v>63</v>
@@ -1946,7 +1946,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="11">
+    <row r="8" spans="1:16" ht="9">
       <c r="A8" s="79"/>
       <c r="B8" s="79" t="s">
         <v>65</v>
@@ -1994,7 +1994,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="11">
+    <row r="9" spans="1:16" ht="9">
       <c r="A9" s="74"/>
       <c r="B9" s="74" t="s">
         <v>60</v>
@@ -2034,7 +2034,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="11">
+    <row r="10" spans="1:16" ht="9">
       <c r="A10" s="19" t="s">
         <v>58</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>5320340</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="11">
+    <row r="11" spans="1:16" ht="9">
       <c r="A11" s="19" t="s">
         <v>57</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>792826</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="11">
+    <row r="12" spans="1:16" ht="9">
       <c r="A12" s="19" t="s">
         <v>56</v>
       </c>
@@ -2184,7 +2184,7 @@
         <v>6053781</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="11">
+    <row r="13" spans="1:16" ht="9">
       <c r="A13" s="19" t="s">
         <v>55</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>2913369</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="11">
+    <row r="14" spans="1:16" ht="9">
       <c r="A14" s="52" t="s">
         <v>54</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>30398249</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="11">
+    <row r="15" spans="1:16" ht="9">
       <c r="A15" s="19" t="s">
         <v>53</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>5350708</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="11">
+    <row r="16" spans="1:16" ht="9">
       <c r="A16" s="19" t="s">
         <v>52</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>2867554</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="11">
+    <row r="17" spans="1:16" ht="9">
       <c r="A17" s="43" t="s">
         <v>51</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>1006135</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="11">
+    <row r="18" spans="1:16" ht="9">
       <c r="A18" s="19" t="s">
         <v>50</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>356537</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="11">
+    <row r="19" spans="1:16" ht="9">
       <c r="A19" s="19" t="s">
         <v>49</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>18464506</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="11">
+    <row r="20" spans="1:16" ht="9">
       <c r="A20" s="19" t="s">
         <v>48</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>8829596</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="11">
+    <row r="21" spans="1:16" ht="9">
       <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>1244935</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="11">
+    <row r="22" spans="1:16" ht="9">
       <c r="A22" s="52" t="s">
         <v>46</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>1917677</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="11">
+    <row r="23" spans="1:16" ht="9">
       <c r="A23" s="19" t="s">
         <v>45</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>10587725</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="11">
+    <row r="24" spans="1:16" ht="9">
       <c r="A24" s="19" t="s">
         <v>44</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>6199901</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="11">
+    <row r="25" spans="1:16" ht="9">
       <c r="A25" s="43" t="s">
         <v>43</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>3787224</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="11">
+    <row r="26" spans="1:16" ht="9">
       <c r="A26" s="19" t="s">
         <v>42</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>2603543</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="11">
+    <row r="27" spans="1:16" ht="9">
       <c r="A27" s="19" t="s">
         <v>41</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>4459685</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="11">
+    <row r="28" spans="1:16" ht="9">
       <c r="A28" s="19" t="s">
         <v>40</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>3861204</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="11">
+    <row r="29" spans="1:16" ht="9">
       <c r="A29" s="19" t="s">
         <v>39</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>1121106</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="11">
+    <row r="30" spans="1:16" ht="9">
       <c r="A30" s="52" t="s">
         <v>38</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>4211377</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="11">
+    <row r="31" spans="1:16" ht="9">
       <c r="A31" s="19" t="s">
         <v>37</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>5036686</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="11">
+    <row r="32" spans="1:16" ht="9">
       <c r="A32" s="19" t="s">
         <v>36</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>8453239</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="11">
+    <row r="33" spans="1:16" ht="9">
       <c r="A33" s="43" t="s">
         <v>35</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>5690749</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="11">
+    <row r="34" spans="1:16" ht="9">
       <c r="A34" s="19" t="s">
         <v>34</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>2058975</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="11">
+    <row r="35" spans="1:16" ht="9">
       <c r="A35" s="19" t="s">
         <v>33</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>5587022</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="11">
+    <row r="36" spans="1:16" ht="9">
       <c r="A36" s="19" t="s">
         <v>32</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>1952553</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="11">
+    <row r="37" spans="1:16" ht="9">
       <c r="A37" s="19" t="s">
         <v>31</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>1935357</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="11">
+    <row r="38" spans="1:16" ht="9">
       <c r="A38" s="52" t="s">
         <v>30</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>2549357</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="11">
+    <row r="39" spans="1:16" ht="9">
       <c r="A39" s="19" t="s">
         <v>29</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>1357535</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="11">
+    <row r="40" spans="1:16" ht="9">
       <c r="A40" s="19" t="s">
         <v>28</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>6006247</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="11">
+    <row r="41" spans="1:16" ht="9">
       <c r="A41" s="43" t="s">
         <v>27</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>1783151</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="11">
+    <row r="42" spans="1:16" ht="9">
       <c r="A42" s="19" t="s">
         <v>26</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>11324755</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="11">
+    <row r="43" spans="1:16" ht="9">
       <c r="A43" s="19" t="s">
         <v>25</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>8739280</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="11">
+    <row r="44" spans="1:16" ht="9">
       <c r="A44" s="19" t="s">
         <v>24</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>899083</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="11">
+    <row r="45" spans="1:16" ht="9">
       <c r="A45" s="19" t="s">
         <v>23</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>10592317</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="11">
+    <row r="46" spans="1:16" ht="9">
       <c r="A46" s="52" t="s">
         <v>22</v>
       </c>
@@ -3884,7 +3884,7 @@
         <v>3730247</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="11">
+    <row r="47" spans="1:16" ht="9">
       <c r="A47" s="19" t="s">
         <v>21</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>4095442</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="11">
+    <row r="48" spans="1:16" ht="9">
       <c r="A48" s="19" t="s">
         <v>20</v>
       </c>
@@ -3984,7 +3984,7 @@
         <v>10690187</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="11">
+    <row r="49" spans="1:16" ht="9">
       <c r="A49" s="43" t="s">
         <v>19</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>866625</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="11">
+    <row r="50" spans="1:16" ht="9">
       <c r="A50" s="19" t="s">
         <v>18</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>4561299</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="11">
+    <row r="51" spans="1:16" ht="9">
       <c r="A51" s="19" t="s">
         <v>17</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>1294282</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="11">
+    <row r="52" spans="1:16" ht="9">
       <c r="A52" s="19" t="s">
         <v>16</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>5855373</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="11">
+    <row r="53" spans="1:16" ht="9">
       <c r="A53" s="19" t="s">
         <v>15</v>
       </c>
@@ -4234,7 +4234,7 @@
         <v>22419490</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="11">
+    <row r="54" spans="1:16" ht="9">
       <c r="A54" s="52" t="s">
         <v>14</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>2479604</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="11">
+    <row r="55" spans="1:16" ht="9">
       <c r="A55" s="19" t="s">
         <v>13</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>607890</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="11">
+    <row r="56" spans="1:16" ht="9">
       <c r="A56" s="19" t="s">
         <v>12</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>7606452</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="11">
+    <row r="57" spans="1:16" ht="9">
       <c r="A57" s="43" t="s">
         <v>11</v>
       </c>
@@ -4434,7 +4434,7 @@
         <v>7257401</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="11">
+    <row r="58" spans="1:16" ht="9">
       <c r="A58" s="19" t="s">
         <v>10</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>1657362</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="11">
+    <row r="59" spans="1:16" ht="9">
       <c r="A59" s="19" t="s">
         <v>9</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>5616271</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="11">
+    <row r="60" spans="1:16" ht="9">
       <c r="A60" s="19" t="s">
         <v>8</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>861028</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="11">
+    <row r="61" spans="1:16" ht="9">
       <c r="A61" s="11" t="s">
         <v>7</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>275913237</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="11">
+    <row r="62" spans="1:16" ht="9">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -4652,7 +4652,7 @@
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
     </row>
-    <row r="63" spans="1:16" ht="39.5" customHeight="1">
+    <row r="63" spans="1:16" ht="39.6" customHeight="1">
       <c r="A63" s="105" t="s">
         <v>6</v>
       </c>
@@ -4724,10 +4724,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.6640625" customWidth="1"/>
+    <col min="2" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6145,10 +6145,10 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.6640625" customWidth="1"/>
+    <col min="2" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
